--- a/05_Figures/Proteome/F1_Overview/c_data/f1_overview_T3.xlsx
+++ b/05_Figures/Proteome/F1_Overview/c_data/f1_overview_T3.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3180" uniqueCount="443">
   <si>
     <t>sheet</t>
   </si>
@@ -839,16 +839,16 @@
     <t>contrasts</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/03_Protein_Contrasts/T3/c_data/protein_contrasts.xlsx</t>
-  </si>
-  <si>
-    <t>cbefccb5a20aca16b8e0561d6f63e2ff</t>
+    <t>03_Group_comparisons/Proteome/02_Protein_Contrasts/T3/c_data/protein_contrasts.xlsx</t>
+  </si>
+  <si>
+    <t>584b4a8ef6e4392af09311cf3cb8db72</t>
   </si>
   <si>
     <t>set_tests</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/04_Set_Contrasts/T3/c_data/set_tests.rds</t>
+    <t>03_Group_comparisons/Proteome/03_Set_Contrasts/T3/c_data/set_tests.rds</t>
   </si>
   <si>
     <t>59addccd8e0b0e73b0e729bf869d80c6</t>
@@ -863,22 +863,22 @@
     <t>bc1bf66e89df936e164c317354990470</t>
   </si>
   <si>
-    <t>00_Input/phenotype.csv</t>
+    <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
     <t>5a1989db406daa0b70189a9f0df52cf3</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/01_Clustering/c_data/clustering.xlsx</t>
-  </si>
-  <si>
-    <t>26ee0be84eef1dc9b7cd280844dda3e8</t>
+    <t>02_Groups/Proteome/c_data/clustering.xlsx</t>
+  </si>
+  <si>
+    <t>8e04a957cceabf91ead651b89d51dd35</t>
   </si>
   <si>
     <t>design</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/02_Design_Contrasts/T3/c_data/design.rds</t>
+    <t>03_Group_comparisons/Proteome/01_Design_Contrasts/T3/c_data/design.rds</t>
   </si>
   <si>
     <t>5b6aabc2a465a28cbc3adbf8fd2c32aa</t>
@@ -989,12 +989,24 @@
     <t>1.2.1</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
     <t>foreach</t>
   </si>
   <si>
@@ -1067,6 +1079,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -1079,6 +1103,15 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -1088,9 +1121,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>limma</t>
   </si>
   <si>
@@ -1127,6 +1157,9 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
     <t>patchwork</t>
   </si>
   <si>
@@ -1205,6 +1238,12 @@
     <t>1.3.0</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -1308,6 +1347,12 @@
   </si>
   <si>
     <t>xml2</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -1835,7 +1880,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -2110,15 +2155,15 @@
         <v>334</v>
       </c>
       <c r="C25" t="s">
-        <v>335</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>335</v>
+      </c>
+      <c r="B26" t="s">
         <v>336</v>
-      </c>
-      <c r="B26" t="s">
-        <v>326</v>
       </c>
       <c r="C26" t="s">
         <v>291</v>
@@ -2132,15 +2177,15 @@
         <v>338</v>
       </c>
       <c r="C27" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B28" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C28" t="s">
         <v>291</v>
@@ -2187,7 +2232,7 @@
         <v>348</v>
       </c>
       <c r="C32" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2242,7 +2287,7 @@
         <v>358</v>
       </c>
       <c r="C37" t="s">
-        <v>335</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2250,7 +2295,7 @@
         <v>359</v>
       </c>
       <c r="B38" t="s">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="C38" t="s">
         <v>291</v>
@@ -2258,10 +2303,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>360</v>
+      </c>
+      <c r="B39" t="s">
         <v>361</v>
-      </c>
-      <c r="B39" t="s">
-        <v>362</v>
       </c>
       <c r="C39" t="s">
         <v>291</v>
@@ -2269,10 +2314,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>362</v>
+      </c>
+      <c r="B40" t="s">
         <v>363</v>
-      </c>
-      <c r="B40" t="s">
-        <v>364</v>
       </c>
       <c r="C40" t="s">
         <v>291</v>
@@ -2280,10 +2325,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
       <c r="C41" t="s">
         <v>291</v>
@@ -2291,32 +2336,32 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B42" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C42" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B43" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C43" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B44" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C44" t="s">
         <v>291</v>
@@ -2324,10 +2369,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B45" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C45" t="s">
         <v>291</v>
@@ -2335,10 +2380,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C46" t="s">
         <v>291</v>
@@ -2346,10 +2391,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C47" t="s">
         <v>291</v>
@@ -2357,10 +2402,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B48" t="s">
-        <v>380</v>
+        <v>338</v>
       </c>
       <c r="C48" t="s">
         <v>291</v>
@@ -2368,10 +2413,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C49" t="s">
         <v>291</v>
@@ -2379,10 +2424,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C50" t="s">
         <v>291</v>
@@ -2390,10 +2435,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B51" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C51" t="s">
         <v>291</v>
@@ -2401,10 +2446,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B52" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C52" t="s">
         <v>291</v>
@@ -2412,10 +2457,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C53" t="s">
         <v>291</v>
@@ -2423,21 +2468,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C54" t="s">
-        <v>335</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B55" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C55" t="s">
         <v>291</v>
@@ -2445,21 +2490,21 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C56" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B57" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C57" t="s">
         <v>291</v>
@@ -2467,10 +2512,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B58" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C58" t="s">
         <v>291</v>
@@ -2478,10 +2523,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B59" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C59" t="s">
         <v>291</v>
@@ -2489,10 +2534,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C60" t="s">
         <v>291</v>
@@ -2500,21 +2545,21 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B61" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C61" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B62" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C62" t="s">
         <v>291</v>
@@ -2522,10 +2567,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B63" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C63" t="s">
         <v>291</v>
@@ -2533,21 +2578,21 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B64" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C64" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B65" t="s">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="C65" t="s">
         <v>291</v>
@@ -2555,10 +2600,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B66" t="s">
-        <v>320</v>
+        <v>413</v>
       </c>
       <c r="C66" t="s">
         <v>291</v>
@@ -2566,10 +2611,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
+        <v>414</v>
+      </c>
+      <c r="B67" t="s">
         <v>415</v>
-      </c>
-      <c r="B67" t="s">
-        <v>416</v>
       </c>
       <c r="C67" t="s">
         <v>291</v>
@@ -2577,10 +2622,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>416</v>
+      </c>
+      <c r="B68" t="s">
         <v>417</v>
-      </c>
-      <c r="B68" t="s">
-        <v>418</v>
       </c>
       <c r="C68" t="s">
         <v>291</v>
@@ -2588,10 +2633,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>418</v>
+      </c>
+      <c r="B69" t="s">
         <v>419</v>
-      </c>
-      <c r="B69" t="s">
-        <v>420</v>
       </c>
       <c r="C69" t="s">
         <v>291</v>
@@ -2599,10 +2644,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>420</v>
+      </c>
+      <c r="B70" t="s">
         <v>421</v>
-      </c>
-      <c r="B70" t="s">
-        <v>422</v>
       </c>
       <c r="C70" t="s">
         <v>291</v>
@@ -2610,21 +2655,21 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>422</v>
+      </c>
+      <c r="B71" t="s">
         <v>423</v>
       </c>
-      <c r="B71" t="s">
-        <v>424</v>
-      </c>
       <c r="C71" t="s">
-        <v>335</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>424</v>
+      </c>
+      <c r="B72" t="s">
         <v>425</v>
-      </c>
-      <c r="B72" t="s">
-        <v>426</v>
       </c>
       <c r="C72" t="s">
         <v>291</v>
@@ -2632,12 +2677,111 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
+        <v>426</v>
+      </c>
+      <c r="B73" t="s">
+        <v>379</v>
+      </c>
+      <c r="C73" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
         <v>427</v>
       </c>
-      <c r="B73" t="s">
-        <v>324</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="B74" t="s">
+        <v>320</v>
+      </c>
+      <c r="C74" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>428</v>
+      </c>
+      <c r="B75" t="s">
+        <v>429</v>
+      </c>
+      <c r="C75" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>430</v>
+      </c>
+      <c r="B76" t="s">
+        <v>431</v>
+      </c>
+      <c r="C76" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>432</v>
+      </c>
+      <c r="B77" t="s">
+        <v>433</v>
+      </c>
+      <c r="C77" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>434</v>
+      </c>
+      <c r="B78" t="s">
+        <v>435</v>
+      </c>
+      <c r="C78" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>436</v>
+      </c>
+      <c r="B79" t="s">
+        <v>437</v>
+      </c>
+      <c r="C79" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>438</v>
+      </c>
+      <c r="B80" t="s">
+        <v>439</v>
+      </c>
+      <c r="C80" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>440</v>
+      </c>
+      <c r="B81" t="s">
+        <v>328</v>
+      </c>
+      <c r="C81" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>441</v>
+      </c>
+      <c r="B82" t="s">
+        <v>442</v>
+      </c>
+      <c r="C82" t="s">
         <v>291</v>
       </c>
     </row>

--- a/05_Figures/Proteome/F1_Overview/c_data/f1_overview_T3.xlsx
+++ b/05_Figures/Proteome/F1_Overview/c_data/f1_overview_T3.xlsx
@@ -842,7 +842,7 @@
     <t>03_Group_comparisons/Proteome/02_Protein_Contrasts/T3/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>584b4a8ef6e4392af09311cf3cb8db72</t>
+    <t>3da19cce14ba77d388a41ecee454b950</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -872,7 +872,7 @@
     <t>02_Groups/Proteome/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>8e04a957cceabf91ead651b89d51dd35</t>
+    <t>65506da788b47182e1478149f673bdfd</t>
   </si>
   <si>
     <t>design</t>
